--- a/data/daily/2026-09/2026-09-13.xlsx
+++ b/data/daily/2026-09/2026-09-13.xlsx
@@ -1170,14 +1170,89 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,110 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,52 +1425,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,154 +1578,54 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2596,21 +2596,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16037</v>
+        <v>16039</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 피곤할 때 섭취 시 기운이 나고 체력이 회복됨</t>
+          <t>확실한 피로 회복 효과 — 기력이 떨어지거나 피로할 때 섭취 시 몸이 가벼워지고 기운이 남.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용 높은 만족도 — 생일이나 응원 선물로 주고받기에 적합함</t>
+          <t>선물용 높은 만족도 — 생일이나 응원 선물로 받았을 때 감동과 실용성을 동시에 제공함.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>우수한 신체 적응도 — 몸에 잘 받고 중요한 일정 시 도움이 됨</t>
+          <t>부담 없는 섭취와 맛 — 맛이 좋고 부담 없이 간편하게 먹기 용이함.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2659,22 +2659,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>활력 증진 및 피로 완화 — 처진 느낌이 덜하고 다음 날 몸이 개운해짐</t>
+          <t>빠른 활력 충전 효과 — 섭취 후 피로감이 덜하고 활력과 정신이 번쩍 드는 느낌을 받음.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>상큼한 맛과 편리한 구성 — 텁텁하지 않은 맛에 액상과 정제로 먹기 편함</t>
+          <t>상큼하고 맛있는 제형 — 건강식품 특유의 텁텁함이 없고 상큼한 맛으로 즐기기 좋음.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>정성스러운 선물 구성 — 포장이 깔끔하고 쇼핑백과 카드가 포함되어 만족스러움</t>
+          <t>간편한 휴대 및 구성 — 정제와 액상이 함께 구성되어 외출이나 여행 시 휴대 및 섭취가 간편함.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>배송 미수령 문제 — 상품을 실제 수령하지 못하는 배송 문제가 발생함</t>
+          <t>배송 문의 중 오류 발생 — 배송기사 연락 시도 과정에서 구매 결정 버튼이 실수로 눌림.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2722,19 +2722,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>지속적인 피로 개선 — 누적된 피로 해소 및 활력 충전에 효과적임</t>
+          <t>우수한 피로 해소 성능 — 지속되는 피로를 풀어주고 기력을 되찾는 데 큰 도움을 줌.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부담 없는 뛰어난 맛 — 거부감 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 상태 — 포장이 고급스러워 선물용으로 매우 적합함</t>
-        </is>
-      </c>
+          <t>고급스러운 선물 포장 — 포장이 고급스럽게 도착하여 자기 자신이나 타인을 위한 선물로 적합함.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2781,17 +2777,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>체력 회복 및 피로 감소 — 힘든 날 먹으면 체력 회복에 도움을 줌</t>
+          <t>간편한 영양 충전 — 여러 영양제를 챙길 필요 없이 한 번에 간편하게 섭취 가능함.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>올인원 간편 복용법 — 여러 영양제를 따로 챙길 필요 없이 한 번에 섭취 가능함</t>
+          <t>체력 회복 및 피로 개선 — 힘들거나 바쁜 날 섭취 시 체력이 회복되고 피로가 덜한 느낌을 줌.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 구성 — 단독 구성으로 추가 증정이 포함되어 실속 있음</t>
+          <t>알찬 추가 증정 구성 — 선물하기 전용 구성으로 추가 2입 증정이 포함되어 혜택이 큼.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2840,25 +2836,25 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>맛있는 과일향 젤리 제형 — 새콤달콤한 맛과 쫄깃한 식감으로 간편하게 챙겨 먹기 좋음</t>
+          <t>맛있는 젤리 형태 — 새콤달콤한 과일 향과 쫄깃한 식감 덕분에 꾸준히 챙겨 먹기 좋음.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>꼼꼼한 포장과 빠른 배송 — 안전한 포장으로 빠르게 전달됨</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>매력적인 사은품 굿즈 — 동봉된 키캡 굿즈의 만족도가 높음</t>
-        </is>
-      </c>
+          <t>꼼꼼한 포장과 배송 — 포장이 꼼꼼하고 배송이 빠르게 완료되어 선물용으로 양호함.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>약간의 씁쓸한 끝맛 — 단맛이 적고 살짝 씁쓸함이 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>키캡 로고 각인 아쉬움 — 증정용 키캡 뒷면에 로고가 표기되어 있어 다소 아쉬움.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>약간의 씁쓸한 맛 — 달지 않고 끝맛에 약간의 씁쓸함이 맴돔.</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -2903,24 +2899,16 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>우수한 활력 충전 효과 — 피로감이 심할 때 컨디션 회복에 큰 도움이 됨</t>
+          <t>뛰어난 피로 개선 체감 — 피로를 자주 느끼는 상황에서 섭취 시 컨디션 회복 효과가 뛰어남.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 섭취 및 휴대성 — 마시기 편하고 가지고 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>마음을 전하는 선물용 — 주변에 건강 응원용으로 전달하기 좋음</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격이 비싸 다소 부담될 수 있음</t>
-        </is>
-      </c>
+          <t>우수한 복용 및 휴대성 — 마시기 편한 제형으로 외출 시 들고 다니며 간편히 섭취함.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2966,19 +2954,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 편의성 — 귀찮음 없이 멀티비타민으로 한 번에 섭취 가능함</t>
+          <t>올인원 섭취의 편의성 — 여러 영양제를 챙기기 귀찮을 때 하나로 간편하게 해결 가능함.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>예쁜 선물용 패키지 — 포장이 이쁘고 주고받기에 부담이 없음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>신속하고 정확한 배송 — 배송이 빠르고 안전하게 도착함</t>
-        </is>
-      </c>
+          <t>예쁜 선물용 포장 — 선물 전용 포장이 예쁘게 되어 있어 부담 없이 전달하기 양호함.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -3025,24 +3009,16 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>피로감 감소 체감 — 피곤할 때 마시면 피로도가 덜함</t>
+          <t>효과적인 피로 감소 — 피곤할 때 마시면 당일 피로감이 줄어들고 기운이 남.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 명절 선물용에 어울리는 고급 포장을 제공함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>기분 좋은 선물 구성 — 젤리 추가 등 귀여운 선물 구성으로 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>부족한 수량 구성 — 꾸준히 먹기에 수량이 적게 느껴짐</t>
-        </is>
-      </c>
+          <t>고급스러운 패키지 구성 — 추석 등의 시즌 패키지가 고급스럽고 젤리 증정이 포함됨.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3084,28 +3060,24 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>액상 분말 일체형 섭취 — 눌러서 가루를 섞어 바로 마실 수 있어 간편함</t>
+          <t>원스톱 복용 방식 — 눌러서 분말과 액상을 섞어 바로 마실 수 있어 편의성이 높음.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>컨디션 개선 효과 — 피로하거나 감기 기운이 있을 때 컨디션 충전에 도움 됨</t>
+          <t>부담 없는 쓴맛과 맛 — 홍삼 제품임에도 쓴맛이 과하지 않고 깔끔하게 섭취할 수 있음.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>실속 있는 증정 구성 — 추가 증정이 포함되어 풍성하게 느껴짐</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>생각보다 큰 제품 용기 — 개별 포장 용기의 크기가 다소 크게 느껴짐</t>
-        </is>
-      </c>
+          <t>신뢰도 높은 브랜드 — 정관장 브랜드로 품질 믿음이 가며 포장도 깔끔함.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3151,22 +3123,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>오래 유지되는 활력 — 지속적인 복용 시 피로가 덜하고 컨디션이 유지됨</t>
+          <t>지속적인 피로 개선 — 꾸준히 섭취 시 피로함이 덜하고 활력 유지 시간이 길어짐.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 휴대 및 섭취성 — 챙겨 먹기 편하고 들고 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>정성 가득한 패키지 — 포장 디자인이 고급스러워 선물용으로 좋음</t>
-        </is>
-      </c>
+          <t>고급스러운 선물 디자인 — 패키지와 디자인 포장이 고급스러워 선물용 만족도가 뛰어남.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>큰 알약 제형 부담 — 알약 크기가 커서 목으로 삼키기 힘들 수 있음</t>
+          <t>큰 정제 크기 목넘김 — 기존 제품 대비 알약 크기가 커서 삼킬 때 다소 불편함.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3214,22 +3182,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 목넘김 — 달지 않아 포 채로 먹거나 물에 타 먹기 편함</t>
+          <t>부담 없는 기분 좋은 맛 — 과하게 달지 않아 포 채로 먹거나 물에 타서 편하게 섭취함.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>혜자로운 사은품 혜택 — 포토카드 등 만족스러운 증정품이 포함됨</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>장 운동 및 소화 보조 — 식후 장 운동 및 건강 관리에 도움을 줌</t>
-        </is>
-      </c>
+          <t>혜자스러운 굿즈 사은품 — 포토카드 등 유용한 사은품이 함께 구성되어 만족도가 큼.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>탄산수 혼합 시 거품 발생 — 탄산수에 부으면 거품이 크게 일어 넘칠 위험이 있음</t>
+          <t>탄산수 혼합 시 거품 넘침 — 탄산수에 타서 마실 경우 거품이 많이 발생하여 넘칠 위험이 있음.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3277,24 +3241,16 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>극찬받는 고급 포장 — 은은한 색감과 정성스러운 포장으로 감동을 줌</t>
+          <t>고급스러운 선물 포장 — 은은한 핑크 빛깔과 정성스러운 포장으로 감동을 줌.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>피부 톤 개선 체감 — 복용 후 피부가 맑아지는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>풍부한 추가 증정 혜택 — 샘플과 추가 앰플 구성으로 실속이 높음</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>초기 효과 체감 미흡 — 섭취 초반에는 즉각적인 변화를 느끼기 어려울 수 있음</t>
-        </is>
-      </c>
+          <t>피부 상태 개선 체감 — 꾸준히 복용 시 피부가 한결 맑아지는 느낌을 받음.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3340,17 +3296,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>특유의 비린 맛 없음 — 단백질 음료 특유의 텁텁함과 비린 맛이 없이 깔끔함</t>
+          <t>비림 없는 진한 풍미 — 단백질 특유의 비리거나 텁텁한 맛이 없으며 초코우유처럼 달콤함.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>운동 후 포만감 제공 — 식사 대용이나 허기 완화에 도움을 줌</t>
+          <t>속 편한 포만감 제공 — 마신 후 속이 더부룩하지 않고 포만감이 있어 간식 대용으로 적절함.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>속 편한 저당 영양 설계 — 당과 칼로리가 낮고 속이 더부룩하지 않음</t>
+          <t>부담 없는 성분 구성 — 당과 칼로리가 낮고 단백질 함량이 높아 운동 후 챙기기 좋음.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3399,22 +3355,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>가성비 뛰어난 패키지 — 저렴한 가격에 많은 양을 구매 가능함</t>
+          <t>질리지 않는 다양한 맛 — 메뉴가 다채롭게 구성되어 매일 먹어도 물리거나 질리지 않음.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>자극적이지 않은 다양한 맛 — 뻑뻑함이 적고 질리지 않는 맛 구성임</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>전자레인지 조리 편의성 — 간편하게 데워 먹을 수 있어 식단 관리에 유용함</t>
-        </is>
-      </c>
+          <t>뛰어난 가성비와 편의성 — 가격이 저렴하고 전자레인지 조리로 간편하게 섭취할 수 있음.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 제품이 녹아서 올 수 있음</t>
+          <t>배송 중 해동 발생 — 배송 도착 시 제품이 완전히 녹아서 오는 경우가 발생함.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3423,7 +3375,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3431,56 +3383,56 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>143</v>
+        <v>858</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>다양한 종류의 메뉴 — 여러 가지 맛이 있어 골라 먹는 재미가 있음</t>
+          <t>고소한 맛과 소화 도움 — 맛이 고소하고 식후 더부룩함을 완화하여 소화에 도움이 됨.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>실속 있는 대용량 구성 — 한 달 간 식단 관리하기에 충분한 수량임</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>유용한 보냉백 사은품 — 증정되는 보냉 파우치의 활용도가 높음</t>
-        </is>
-      </c>
+          <t>합리적인 특가 구매 — 보너스 증정 및 특가 행사를 통해 저렴하게 구매할 수 있음.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 수령 시 제품이 다소 녹아 있을 수 있음</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>미배송 처리 누락 — 주문 후 실제로 상품을 배송받지 못하는 문제가 발생함.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>복용 초기 장 반응 — 섭취 후 뱃속 소리나 방귀가 자주 발생하는 가스 반응이 나타남.</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
@@ -3494,58 +3446,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1900</v>
+        <v>143</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 근회복과 활력 증진에 효과를 체감함</t>
+          <t>다양한 종류와 맛 — 여러 맛으로 구성되어 골라 먹기 좋고 맛의 만족도가 높음.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>음료 혼합 및 복용 용이 — 물이나 음료에 타 먹기 부담이 없음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>귀여운 키링 사은품 — 동봉된 키링 굿즈의 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>실용적인 보냉백 증정 — 도시락을 싸 다니기 좋은 사이즈의 보냉 파우치가 함께 제공됨.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>배송 시 제품 해동 — 배송 상태에서 냉동 제품이 많이 녹아 도착함.</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3553,60 +3505,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>858</v>
+        <v>1901</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고소한 맛과 적당한 용량 — 맛이 고소하고 한 번에 섭취하기 알맞음</t>
+          <t>운동 수행 및 근회복 도움 — 운동할 때 카페인 대체용으로 좋으며 근육 회복과 활력에 도움 됨.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>저렴한 특가 구매 혜택 — 추가 포 수량과 사은품을 합리적인 가격에 구매 가능함</t>
+          <t>쉽고 편한 음용 형태 — 물이나 음료에 섞어 먹기 부담스럽지 않고 간편함.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>고급스러운 제품 포장 — 패키지가 깔끔하여 선물용으로 좋음</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>복용 초기 복부 반응 — 섭취 초기에 뱃속이 더부룩하거나 가스가 찰 수 있음</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>배송 누락 사고 — 제품을 정상 수령하지 못했다는 의견이 있음</t>
-        </is>
-      </c>
+          <t>귀여운 키링 사은품 — 동봉된 키링 사은품의 디자인이 만족스러움.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
@@ -3651,19 +3595,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>더부룩함 개선 및 소화 — 식후 속 답답함이 줄고 소화에 큰 도움이 됨</t>
+          <t>확실한 소화 및 배변 개선 — 식후 더부룩함이 덜하고 묵직한 속을 편안하게 해 주며 배변에 도움 됨.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>고소한 군고구마 풍미 — 고소하고 부담 없는 맛으로 쉽게 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>원활한 배변 활동 지원 — 매일 꾸준히 먹으면 배변 활동에 효과적임</t>
-        </is>
-      </c>
+          <t>부담 없는 군고구마 맛 — 군고구마 풍미로 거부감 없이 고소하게 먹을 수 있음.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3710,17 +3650,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>확실한 활력 및 피로 개선 — 아침에 일어날 때 몸이 가볍고 운동 시 지치지 않음</t>
+          <t>효과적인 활력 시너지 — 아르기닌과 밀크씨슬(마카) 조합으로 피로가 쌓였을 때 에너지를 줌.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>알찬 2종 조합 세트 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 유용함</t>
+          <t>체감되는 피로 완화 — 아침 일어날 때 몸이 한결 가볍고 일상 및 운동 시 지치지 않음.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고급 쇼핑백 증정 — 선물용 전용 쇼핑백이 포함되어 깔끔함</t>
+          <t>선물용 쇼핑백 제공 — 2개월분의 알찬 용량과 쇼핑백 증정으로 선물하기에 최적화됨.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3730,7 +3670,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3738,50 +3678,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌 함유 — 1포당 높은 함량으로 에너지 충전에 효과적임</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>지구력 및 컨디션 상승 — 운동 및 일상생활 중 체력 유지에 큰 도움 됨</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>위생적인 개별 포장 — 휴대가 편리하고 필요할 때 바로 먹기 편함</t>
-        </is>
-      </c>
+          <t>우수한 숙취 해소 효능 — 섭취 시 숙취 해소 효과가 매우 뛰어남.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4104,7 +4036,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16037</v>
+        <v>16039</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15372</v>
@@ -4128,7 +4060,7 @@
         <v>2612</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>769</v>
@@ -4142,76 +4074,70 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 피곤할 때 섭취 시 기운이 나고 체력이 회복됨
-선물용 높은 만족도 — 생일이나 응원 선물로 주고받기에 적합함
-우수한 신체 적응도 — 몸에 잘 받고 중요한 일정 시 도움이 됨</t>
+          <t>확실한 피로 회복 효과 — 기력이 떨어지거나 피로할 때 섭취 시 몸이 가벼워지고 기운이 남.
+선물용 높은 만족도 — 생일이나 응원 선물로 받았을 때 감동과 실용성을 동시에 제공함.
+부담 없는 섭취와 맛 — 맛이 좋고 부담 없이 간편하게 먹기 용이함.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>활력 증진 및 피로 완화 — 처진 느낌이 덜하고 다음 날 몸이 개운해짐
-상큼한 맛과 편리한 구성 — 텁텁하지 않은 맛에 액상과 정제로 먹기 편함
-정성스러운 선물 구성 — 포장이 깔끔하고 쇼핑백과 카드가 포함되어 만족스러움</t>
+          <t>빠른 활력 충전 효과 — 섭취 후 피로감이 덜하고 활력과 정신이 번쩍 드는 느낌을 받음.
+상큼하고 맛있는 제형 — 건강식품 특유의 텁텁함이 없고 상큼한 맛으로 즐기기 좋음.
+간편한 휴대 및 구성 — 정제와 액상이 함께 구성되어 외출이나 여행 시 휴대 및 섭취가 간편함.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>지속적인 피로 개선 — 누적된 피로 해소 및 활력 충전에 효과적임
-부담 없는 뛰어난 맛 — 거부감 없이 맛있게 먹을 수 있음
-고급스러운 포장 상태 — 포장이 고급스러워 선물용으로 매우 적합함</t>
+          <t>우수한 피로 해소 성능 — 지속되는 피로를 풀어주고 기력을 되찾는 데 큰 도움을 줌.
+고급스러운 선물 포장 — 포장이 고급스럽게 도착하여 자기 자신이나 타인을 위한 선물로 적합함.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>체력 회복 및 피로 감소 — 힘든 날 먹으면 체력 회복에 도움을 줌
-올인원 간편 복용법 — 여러 영양제를 따로 챙길 필요 없이 한 번에 섭취 가능함
-알찬 추가 증정 구성 — 단독 구성으로 추가 증정이 포함되어 실속 있음</t>
+          <t>간편한 영양 충전 — 여러 영양제를 챙길 필요 없이 한 번에 간편하게 섭취 가능함.
+체력 회복 및 피로 개선 — 힘들거나 바쁜 날 섭취 시 체력이 회복되고 피로가 덜한 느낌을 줌.
+알찬 추가 증정 구성 — 선물하기 전용 구성으로 추가 2입 증정이 포함되어 혜택이 큼.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 과일향 젤리 제형 — 새콤달콤한 맛과 쫄깃한 식감으로 간편하게 챙겨 먹기 좋음
-꼼꼼한 포장과 빠른 배송 — 안전한 포장으로 빠르게 전달됨
-매력적인 사은품 굿즈 — 동봉된 키캡 굿즈의 만족도가 높음</t>
+          <t>맛있는 젤리 형태 — 새콤달콤한 과일 향과 쫄깃한 식감 덕분에 꾸준히 챙겨 먹기 좋음.
+꼼꼼한 포장과 배송 — 포장이 꼼꼼하고 배송이 빠르게 완료되어 선물용으로 양호함.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>우수한 활력 충전 효과 — 피로감이 심할 때 컨디션 회복에 큰 도움이 됨
-간편한 섭취 및 휴대성 — 마시기 편하고 가지고 다니기 용이함
-마음을 전하는 선물용 — 주변에 건강 응원용으로 전달하기 좋음</t>
+          <t>뛰어난 피로 개선 체감 — 피로를 자주 느끼는 상황에서 섭취 시 컨디션 회복 효과가 뛰어남.
+우수한 복용 및 휴대성 — 마시기 편한 제형으로 외출 시 들고 다니며 간편히 섭취함.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 편의성 — 귀찮음 없이 멀티비타민으로 한 번에 섭취 가능함
-예쁜 선물용 패키지 — 포장이 이쁘고 주고받기에 부담이 없음
-신속하고 정확한 배송 — 배송이 빠르고 안전하게 도착함</t>
+          <t>올인원 섭취의 편의성 — 여러 영양제를 챙기기 귀찮을 때 하나로 간편하게 해결 가능함.
+예쁜 선물용 포장 — 선물 전용 포장이 예쁘게 되어 있어 부담 없이 전달하기 양호함.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>피로감 감소 체감 — 피곤할 때 마시면 피로도가 덜함
-고급스러운 패키지 디자인 — 명절 선물용에 어울리는 고급 포장을 제공함
-기분 좋은 선물 구성 — 젤리 추가 등 귀여운 선물 구성으로 만족도가 높음</t>
+          <t>효과적인 피로 감소 — 피곤할 때 마시면 당일 피로감이 줄어들고 기운이 남.
+고급스러운 패키지 구성 — 추석 등의 시즌 패키지가 고급스럽고 젤리 증정이 포함됨.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>액상 분말 일체형 섭취 — 눌러서 가루를 섞어 바로 마실 수 있어 간편함
-컨디션 개선 효과 — 피로하거나 감기 기운이 있을 때 컨디션 충전에 도움 됨
-실속 있는 증정 구성 — 추가 증정이 포함되어 풍성하게 느껴짐</t>
+          <t>원스톱 복용 방식 — 눌러서 분말과 액상을 섞어 바로 마실 수 있어 편의성이 높음.
+부담 없는 쓴맛과 맛 — 홍삼 제품임에도 쓴맛이 과하지 않고 깔끔하게 섭취할 수 있음.
+신뢰도 높은 브랜드 — 정관장 브랜드로 품질 믿음이 가며 포장도 깔끔함.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>오래 유지되는 활력 — 지속적인 복용 시 피로가 덜하고 컨디션이 유지됨
-우수한 휴대 및 섭취성 — 챙겨 먹기 편하고 들고 다니기 용이함
-정성 가득한 패키지 — 포장 디자인이 고급스러워 선물용으로 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>지속적인 피로 개선 — 꾸준히 섭취 시 피로함이 덜하고 활력 유지 시간이 길어짐.
+고급스러운 선물 디자인 — 패키지와 디자인 포장이 고급스러워 선물용 만족도가 뛰어남.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4220,35 +4146,24 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>배송 미수령 문제 — 상품을 실제 수령하지 못하는 배송 문제가 발생함</t>
+          <t>배송 문의 중 오류 발생 — 배송기사 연락 시도 과정에서 구매 결정 버튼이 실수로 눌림.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>약간의 씁쓸한 끝맛 — 단맛이 적고 살짝 씁쓸함이 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격이 비싸 다소 부담될 수 있음</t>
-        </is>
-      </c>
+          <t>키캡 로고 각인 아쉬움 — 증정용 키캡 뒷면에 로고가 표기되어 있어 다소 아쉬움.
+약간의 씁쓸한 맛 — 달지 않고 끝맛에 약간의 씁쓸함이 맴돔.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>부족한 수량 구성 — 꾸준히 먹기에 수량이 적게 느껴짐</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>생각보다 큰 제품 용기 — 개별 포장 용기의 크기가 다소 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>큰 알약 제형 부담 — 알약 크기가 커서 목으로 삼키기 힘들 수 있음</t>
+          <t>큰 정제 크기 목넘김 — 기존 제품 대비 알약 크기가 커서 삼킬 때 다소 불편함.</t>
         </is>
       </c>
     </row>
@@ -4468,32 +4383,32 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -4525,24 +4440,24 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
@@ -4550,7 +4465,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
     </row>
@@ -4582,19 +4497,19 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
-        </is>
-      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
@@ -4607,7 +4522,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4582,13 @@
         <v>50</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>858</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>1900</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>858</v>
+        <v>1901</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>1654</v>
@@ -4682,7 +4597,7 @@
         <v>1534</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4693,72 +4608,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 목넘김 — 달지 않아 포 채로 먹거나 물에 타 먹기 편함
-혜자로운 사은품 혜택 — 포토카드 등 만족스러운 증정품이 포함됨
-장 운동 및 소화 보조 — 식후 장 운동 및 건강 관리에 도움을 줌</t>
+          <t>부담 없는 기분 좋은 맛 — 과하게 달지 않아 포 채로 먹거나 물에 타서 편하게 섭취함.
+혜자스러운 굿즈 사은품 — 포토카드 등 유용한 사은품이 함께 구성되어 만족도가 큼.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>극찬받는 고급 포장 — 은은한 색감과 정성스러운 포장으로 감동을 줌
-피부 톤 개선 체감 — 복용 후 피부가 맑아지는 느낌을 받음
-풍부한 추가 증정 혜택 — 샘플과 추가 앰플 구성으로 실속이 높음</t>
+          <t>고급스러운 선물 포장 — 은은한 핑크 빛깔과 정성스러운 포장으로 감동을 줌.
+피부 상태 개선 체감 — 꾸준히 복용 시 피부가 한결 맑아지는 느낌을 받음.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>특유의 비린 맛 없음 — 단백질 음료 특유의 텁텁함과 비린 맛이 없이 깔끔함
-운동 후 포만감 제공 — 식사 대용이나 허기 완화에 도움을 줌
-속 편한 저당 영양 설계 — 당과 칼로리가 낮고 속이 더부룩하지 않음</t>
+          <t>비림 없는 진한 풍미 — 단백질 특유의 비리거나 텁텁한 맛이 없으며 초코우유처럼 달콤함.
+속 편한 포만감 제공 — 마신 후 속이 더부룩하지 않고 포만감이 있어 간식 대용으로 적절함.
+부담 없는 성분 구성 — 당과 칼로리가 낮고 단백질 함량이 높아 운동 후 챙기기 좋음.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>가성비 뛰어난 패키지 — 저렴한 가격에 많은 양을 구매 가능함
-자극적이지 않은 다양한 맛 — 뻑뻑함이 적고 질리지 않는 맛 구성임
-전자레인지 조리 편의성 — 간편하게 데워 먹을 수 있어 식단 관리에 유용함</t>
+          <t>질리지 않는 다양한 맛 — 메뉴가 다채롭게 구성되어 매일 먹어도 물리거나 질리지 않음.
+뛰어난 가성비와 편의성 — 가격이 저렴하고 전자레인지 조리로 간편하게 섭취할 수 있음.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>다양한 종류의 메뉴 — 여러 가지 맛이 있어 골라 먹는 재미가 있음
-실속 있는 대용량 구성 — 한 달 간 식단 관리하기에 충분한 수량임
-유용한 보냉백 사은품 — 증정되는 보냉 파우치의 활용도가 높음</t>
+          <t>고소한 맛과 소화 도움 — 맛이 고소하고 식후 더부룩함을 완화하여 소화에 도움이 됨.
+합리적인 특가 구매 — 보너스 증정 및 특가 행사를 통해 저렴하게 구매할 수 있음.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 근회복과 활력 증진에 효과를 체감함
-음료 혼합 및 복용 용이 — 물이나 음료에 타 먹기 부담이 없음
-귀여운 키링 사은품 — 동봉된 키링 굿즈의 만족도가 높음</t>
+          <t>다양한 종류와 맛 — 여러 맛으로 구성되어 골라 먹기 좋고 맛의 만족도가 높음.
+실용적인 보냉백 증정 — 도시락을 싸 다니기 좋은 사이즈의 보냉 파우치가 함께 제공됨.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>고소한 맛과 적당한 용량 — 맛이 고소하고 한 번에 섭취하기 알맞음
-저렴한 특가 구매 혜택 — 추가 포 수량과 사은품을 합리적인 가격에 구매 가능함
-고급스러운 제품 포장 — 패키지가 깔끔하여 선물용으로 좋음</t>
+          <t>운동 수행 및 근회복 도움 — 운동할 때 카페인 대체용으로 좋으며 근육 회복과 활력에 도움 됨.
+쉽고 편한 음용 형태 — 물이나 음료에 섞어 먹기 부담스럽지 않고 간편함.
+귀여운 키링 사은품 — 동봉된 키링 사은품의 디자인이 만족스러움.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 개선 및 소화 — 식후 속 답답함이 줄고 소화에 큰 도움이 됨
-고소한 군고구마 풍미 — 고소하고 부담 없는 맛으로 쉽게 복용 가능함
-원활한 배변 활동 지원 — 매일 꾸준히 먹으면 배변 활동에 효과적임</t>
+          <t>확실한 소화 및 배변 개선 — 식후 더부룩함이 덜하고 묵직한 속을 편안하게 해 주며 배변에 도움 됨.
+부담 없는 군고구마 맛 — 군고구마 풍미로 거부감 없이 고소하게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 및 피로 개선 — 아침에 일어날 때 몸이 가볍고 운동 시 지치지 않음
-알찬 2종 조합 세트 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 유용함
-고급 쇼핑백 증정 — 선물용 전용 쇼핑백이 포함되어 깔끔함</t>
+          <t>효과적인 활력 시너지 — 아르기닌과 밀크씨슬(마카) 조합으로 피로가 쌓였을 때 에너지를 줌.
+체감되는 피로 완화 — 아침 일어날 때 몸이 한결 가볍고 일상 및 운동 시 지치지 않음.
+선물용 쇼핑백 제공 — 2개월분의 알찬 용량과 쇼핑백 증정으로 선물하기에 최적화됨.</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌 함유 — 1포당 높은 함량으로 에너지 충전에 효과적임
-지구력 및 컨디션 상승 — 운동 및 일상생활 중 체력 유지에 큰 도움 됨
-위생적인 개별 포장 — 휴대가 편리하고 필요할 때 바로 먹기 편함</t>
+          <t>우수한 숙취 해소 효능 — 섭취 시 숙취 해소 효과가 매우 뛰어남.</t>
         </is>
       </c>
     </row>
@@ -4770,32 +4677,28 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>탄산수 혼합 시 거품 발생 — 탄산수에 부으면 거품이 크게 일어 넘칠 위험이 있음</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>초기 효과 체감 미흡 — 섭취 초반에는 즉각적인 변화를 느끼기 어려울 수 있음</t>
-        </is>
-      </c>
+          <t>탄산수 혼합 시 거품 넘침 — 탄산수에 타서 마실 경우 거품이 많이 발생하여 넘칠 위험이 있음.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 제품이 녹아서 올 수 있음</t>
+          <t>배송 중 해동 발생 — 배송 도착 시 제품이 완전히 녹아서 오는 경우가 발생함.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 수령 시 제품이 다소 녹아 있을 수 있음</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>복용 초기 복부 반응 — 섭취 초기에 뱃속이 더부룩하거나 가스가 찰 수 있음
-배송 누락 사고 — 제품을 정상 수령하지 못했다는 의견이 있음</t>
-        </is>
-      </c>
+          <t>미배송 처리 누락 — 주문 후 실제로 상품을 배송받지 못하는 문제가 발생함.
+복용 초기 장 반응 — 섭취 후 뱃속 소리나 방귀가 자주 발생하는 가스 반응이 나타남.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>배송 시 제품 해동 — 배송 상태에서 냉동 제품이 많이 녹아 도착함.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
@@ -4828,19 +4731,19 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>49,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>46,900원</t>
@@ -4853,7 +4756,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -5043,7 +4946,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5051,12 +4954,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5066,47 +4969,35 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>980</v>
+        <v>6278</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>배변 활동 원활 보조 — 복용 후 화장실을 가고 배출이 잘 되는 느낌임</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>간식 같은 맛과 제형 — 출출할 때 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>저렴한 구매 가격 — 부담 없는 가성비로 접근하기 편함</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>다이어트 효과 미체감 — 탄수화물 및 지방 억제 효과는 체감하기 어려움</t>
-        </is>
-      </c>
+          <t>압도적인 가격 경쟁력 — 동일 성분 대비 가격이 매우 저렴하여 재구매율이 높음.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5114,12 +5005,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5129,38 +5020,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>38</v>
+        <v>6146</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>저렴한 침향환 입문용 — 가격 부담 없이 침향환을 경험해 보기 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>고급스러운 포장과 보증서 — 품질보증서가 포함되어 있고 포장이 고급스러움</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>상승하는 기력 체감 — 복용 후 기운이 오르고 열을 진정시키는 데 도움 됨</t>
-        </is>
-      </c>
+          <t>가성비와 알찬 성분 — 가격이 저렴하면서 성분 함량이 만족스러워 꾸준히 구매함.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>배송 중 포장 훼손 — 박스 모서리가 찢어지거나 테이프가 잘려 배송될 수 있음</t>
+          <t>복용 후 내장 통증 — 섭취 시 위나 췌장 부위에 통증이 발생하여 복용을 중단함.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5169,7 +5052,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5177,58 +5060,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306209&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/rS9JgHwoY8ffaFGoRZTx032306209_00_01rS9JgHwoY8ffaFGoRZTx.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>4548</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 섭취 편의성 — 맛이 좋아 취침 전 간식처럼 먹기 편함</t>
+          <t>저렴한 구매 가격 — 가격 부담이 없어 자주 이용 및 재구매하기에 적절함.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>미세한 정서 안정 효과 — 꾸준히 먹으면 일정 부분 도움이 되는 느낌임</t>
+          <t>편리한 사용성 — 챙겨 먹기 편리하며 복용 후 전반적인 만족도가 높음.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>단기 효과 체감 미흡 — 맛은 좋으나 즉각적인 효과를 알기 어려움</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5236,58 +5115,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 글루타치온 PDRN 구미 7일분</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306205&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/3ZIc8SM52diH1RyBcU9M032306205_00_013ZIc8SM52diH1RyBcU9M.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>1059</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형 — 단것이 당길 때 간식 대용으로 맛있게 먹을 수 있음</t>
+          <t>합리적 가성비와 활력 — 저렴한 가격으로 활력을 챙기기 좋고 맛도 훌륭함.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 생기 충전 — 하루 한 알씩 쉽게 영양을 챙김</t>
+          <t>넉넉한 양과 꼼꼼한 포장 — 포장이 꼼꼼하고 양이 넉넉하여 만족스러움.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>아쉬운 제품 용량 — 맛에 비해 전체적인 양이 다소 적게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5295,58 +5170,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>421</v>
+        <v>3314</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>즉각적인 변비 개선 — 마신 후 신속하게 화장실 반응이 올 정도로 효과적임</t>
+          <t>높은 함량과 저렴한 가격 — 다이소 특유의 저렴함에 성분 함량이 높아 추천할 만함.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>높은 접근성과 가성비 — 다이소에서 저렴하고 빠르게 구매 가능함</t>
+          <t>편리한 섭취 및 건강 도움 — 잇몸 건강에 도움이 되며 사용하기 편리함.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>강한 단맛과 호불호 — 새콤하지만 단맛이 다소 강함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5354,12 +5225,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5369,43 +5240,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>717</v>
+        <v>1505</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>압도적인 초가성비 — 30일 분량을 매우 저렴한 가격으로 챙길 수 있음</t>
+          <t>확실한 배변 활동 개선 — 복용 후 화장실을 쉽게 가게 되어 장 건강 관리에 효과적임.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>부담 없는 정제 크기 — 알약 크기가 많이 크지 않아 복용하기 수월함</t>
+          <t>작은 정제와 휴대용 용기 — 알약 크기가 작아 삼키기 편하고 전용 용기로 휴대성이 양호함.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>즉각적 체감 효과 부족 — 꾸준히 먹어도 뚜렷한 피로 회복 체감이 적을 수 있음</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5413,12 +5280,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5428,36 +5295,36 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>1195</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>정성스러운 낱개 포장 — 한 알씩 깔끔하게 포장되어 위생적임</t>
+          <t>상쾌한 포카리 맛 — 물을 많이 타서 마셔도 포카리스웨트 맛이 나 음용하기 좋음.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>가벼운 선물용 적합 — 명절이나 기념일에 가볍게 선물하기에 부담 없음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>우수한 가성비 구성 — 홍삼 제품을 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>간편한 타 먹는 방식 — 들고 다니며 붓기 관리나 수분/전해질 충전용으로 타 마시기 편함.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>개인차 있는 맛 기호 — 맛이 입에 맞지 않아 재구매 의사가 떨어지는 편임.</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -5472,7 +5339,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 에너지샷 5포</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5482,39 +5349,39 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000197&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250813/V9qCJdlaEC8Ugb1xrzDE600000197_00_00V9qCJdlaEC8Ugb1xrzDE.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>402</v>
+        <v>2298</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>강력한 피로 회복 — 비타민 B 함유로 활력을 높이는 데 효과적임</t>
+          <t>저렴한 가격과 복용 편의 — 다이소에서 저렴하게 살 수 있고 챙겨 먹기 편함.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>휴대하기 좋은 액상 포 — 여행이나 외출 시 간단히 챙겨 먹기 편함</t>
+          <t>생리통 완화 도움 — 생리통이 심할 때 섭취 시 완화 효과를 체감함.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>불편한 포장 절단성 — 이지컷 방식이 아니어서 개봉하기 뻑뻑할 수 있음</t>
+          <t>자주 발생하는 품절 — 인기 상품으로 인해 매장 및 온라인에 품절이 자주 뜸.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -5523,7 +5390,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5531,12 +5398,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5546,28 +5413,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1482</v>
+        <v>3374</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>알약 대체 구미 제형 — 알약을 잘 못 삼키는 사람도 젤리처럼 편하게 먹음</t>
+          <t>부담 없는 가성비 함량 — 가격 부담이 없고 대웅제약 제조로 성분 함량이 훌륭함.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>상큼하고 좋은 향과 맛 — 맛이 좋아 매일 잊지 않고 챙겨 먹기 좋음</t>
+          <t>피로감 개선 효과 — 매일 섭취 시 피곤함이 줄어드는 효과를 체감함.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -5578,7 +5445,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5586,56 +5453,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 타우린샷 5포</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591440&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250514/waK43E1bo4dCUhjXdTRE591591440_00_00waK43E1bo4dCUhjXdTRE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>2827</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>단기 에너지 충전 — 피곤하고 지칠 때 먹으면 졸음이 덜하고 에너지가 생김</t>
+          <t>약사 추천 일일 권장량 — 필요 하루 권장량이 충실히 포함되어 있어 신뢰도가 높음.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>여행용 간편 휴대 — 외부 활동이나 여행 시 챙겨 먹기 편리함</t>
+          <t>햇빛 부족 환경 보충 — 재택근무 등으로 햇빛 보충이 어려운 경우 섭취하기 유용함.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>용량 대비 비싼 가격 — 5포 구성 대비 가격이 다소 비싸게 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>매장 재고 부족 — 일부 동네 매장에서는 재구매가 어려울 수 있음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5749,52 +5608,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>비타민D</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -5806,37 +5665,37 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -5846,12 +5705,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -5863,52 +5722,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 글루타치온 PDRN 구미 7일분</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 에너지샷 5포</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 타우린샷 5포</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5919,25 +5778,25 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
@@ -5956,37 +5815,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>980</v>
+        <v>6278</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>38</v>
+        <v>6146</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>348</v>
+        <v>4548</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>646</v>
+        <v>1059</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>421</v>
+        <v>3314</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>717</v>
+        <v>1505</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>24</v>
+        <v>1195</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>402</v>
+        <v>2298</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1482</v>
+        <v>3374</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5994,117 +5853,91 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>배변 활동 원활 보조 — 복용 후 화장실을 가고 배출이 잘 되는 느낌임
-간식 같은 맛과 제형 — 출출할 때 부담 없이 먹기 좋음
-저렴한 구매 가격 — 부담 없는 가성비로 접근하기 편함</t>
+          <t>압도적인 가격 경쟁력 — 동일 성분 대비 가격이 매우 저렴하여 재구매율이 높음.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 침향환 입문용 — 가격 부담 없이 침향환을 경험해 보기 좋음
-고급스러운 포장과 보증서 — 품질보증서가 포함되어 있고 포장이 고급스러움
-상승하는 기력 체감 — 복용 후 기운이 오르고 열을 진정시키는 데 도움 됨</t>
+          <t>가성비와 알찬 성분 — 가격이 저렴하면서 성분 함량이 만족스러워 꾸준히 구매함.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 섭취 편의성 — 맛이 좋아 취침 전 간식처럼 먹기 편함
-미세한 정서 안정 효과 — 꾸준히 먹으면 일정 부분 도움이 되는 느낌임</t>
+          <t>저렴한 구매 가격 — 가격 부담이 없어 자주 이용 및 재구매하기에 적절함.
+편리한 사용성 — 챙겨 먹기 편리하며 복용 후 전반적인 만족도가 높음.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형 — 단것이 당길 때 간식 대용으로 맛있게 먹을 수 있음
-간편한 생기 충전 — 하루 한 알씩 쉽게 영양을 챙김</t>
+          <t>합리적 가성비와 활력 — 저렴한 가격으로 활력을 챙기기 좋고 맛도 훌륭함.
+넉넉한 양과 꼼꼼한 포장 — 포장이 꼼꼼하고 양이 넉넉하여 만족스러움.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>즉각적인 변비 개선 — 마신 후 신속하게 화장실 반응이 올 정도로 효과적임
-높은 접근성과 가성비 — 다이소에서 저렴하고 빠르게 구매 가능함</t>
+          <t>높은 함량과 저렴한 가격 — 다이소 특유의 저렴함에 성분 함량이 높아 추천할 만함.
+편리한 섭취 및 건강 도움 — 잇몸 건강에 도움이 되며 사용하기 편리함.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 초가성비 — 30일 분량을 매우 저렴한 가격으로 챙길 수 있음
-부담 없는 정제 크기 — 알약 크기가 많이 크지 않아 복용하기 수월함</t>
+          <t>확실한 배변 활동 개선 — 복용 후 화장실을 쉽게 가게 되어 장 건강 관리에 효과적임.
+작은 정제와 휴대용 용기 — 알약 크기가 작아 삼키기 편하고 전용 용기로 휴대성이 양호함.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>정성스러운 낱개 포장 — 한 알씩 깔끔하게 포장되어 위생적임
-가벼운 선물용 적합 — 명절이나 기념일에 가볍게 선물하기에 부담 없음
-우수한 가성비 구성 — 홍삼 제품을 저렴한 가격에 구매 가능함</t>
+          <t>상쾌한 포카리 맛 — 물을 많이 타서 마셔도 포카리스웨트 맛이 나 음용하기 좋음.
+간편한 타 먹는 방식 — 들고 다니며 붓기 관리나 수분/전해질 충전용으로 타 마시기 편함.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>강력한 피로 회복 — 비타민 B 함유로 활력을 높이는 데 효과적임
-휴대하기 좋은 액상 포 — 여행이나 외출 시 간단히 챙겨 먹기 편함</t>
+          <t>저렴한 가격과 복용 편의 — 다이소에서 저렴하게 살 수 있고 챙겨 먹기 편함.
+생리통 완화 도움 — 생리통이 심할 때 섭취 시 완화 효과를 체감함.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>알약 대체 구미 제형 — 알약을 잘 못 삼키는 사람도 젤리처럼 편하게 먹음
-상큼하고 좋은 향과 맛 — 맛이 좋아 매일 잊지 않고 챙겨 먹기 좋음</t>
+          <t>부담 없는 가성비 함량 — 가격 부담이 없고 대웅제약 제조로 성분 함량이 훌륭함.
+피로감 개선 효과 — 매일 섭취 시 피곤함이 줄어드는 효과를 체감함.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>단기 에너지 충전 — 피곤하고 지칠 때 먹으면 졸음이 덜하고 에너지가 생김
-여행용 간편 휴대 — 외부 활동이나 여행 시 챙겨 먹기 편리함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>약사 추천 일일 권장량 — 필요 하루 권장량이 충실히 포함되어 있어 신뢰도가 높음.
+햇빛 부족 환경 보충 — 재택근무 등으로 햇빛 보충이 어려운 경우 섭취하기 유용함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>다이어트 효과 미체감 — 탄수화물 및 지방 억제 효과는 체감하기 어려움</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>배송 중 포장 훼손 — 박스 모서리가 찢어지거나 테이프가 잘려 배송될 수 있음</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>단기 효과 체감 미흡 — 맛은 좋으나 즉각적인 효과를 알기 어려움</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>아쉬운 제품 용량 — 맛에 비해 전체적인 양이 다소 적게 느껴짐</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>강한 단맛과 호불호 — 새콤하지만 단맛이 다소 강함</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>즉각적 체감 효과 부족 — 꾸준히 먹어도 뚜렷한 피로 회복 체감이 적을 수 있음</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>복용 후 내장 통증 — 섭취 시 위나 췌장 부위에 통증이 발생하여 복용을 중단함.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>개인차 있는 맛 기호 — 맛이 입에 맞지 않아 재구매 의사가 떨어지는 편임.</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>불편한 포장 절단성 — 이지컷 방식이 아니어서 개봉하기 뻑뻑할 수 있음</t>
+          <t>자주 발생하는 품절 — 인기 상품으로 인해 매장 및 온라인에 품절이 자주 뜸.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>용량 대비 비싼 가격 — 5포 구성 대비 가격이 다소 비싸게 느껴질 수 있음
-매장 재고 부족 — 일부 동네 매장에서는 재구매가 어려울 수 있음</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6124,17 +5957,17 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -6149,17 +5982,17 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6346,50 +6179,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 매드 MAD 10일 (+2일)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>이너랩</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254467&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5374</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>수면의 질 개선 보조 — 뒤척임 없이 빠르게 숙면에 들도록 도와줌</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>장거리 여행 필수품 — 비행이나 여행 시 수면을 위해 챙기기 좋음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>식물성 안심 원료 — 식약처 인정 식물성 원료로 부담 없이 섭취 가능함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025446726ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -6405,58 +6222,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[올영단독 증량기획] 셀트리온 홀드잇 매드 MAD 10일 (+2일)</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>이너랩</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254467&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025446726ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>3088</v>
+        <v>5376</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>하루 1알 간편 관리 — 여러 번 챙길 필요 없이 하루 1알로 관리가 가능함</t>
+          <t>수면 진입 시간 단축 — 한 포 섭취 후 평소보다 훨씬 빠르고 수월하게 잠에 듦.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 가방이나 파우치에 넣고 다니기 편함</t>
+          <t>장거리 비행 필수템 — 장거리 이동이나 비행 시 편안한 숙면을 취하도록 도움.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>섭취 후 복부 온열감 — 원료 특성상 복용 후 속에서 따뜻한 느낌이 들 수 있음</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6464,48 +6277,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>467</v>
+        <v>22045</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>장 케어와 체지방 동시 관리 — 유산균 기능과 다이어트 관리를 동시에 수행함</t>
+          <t>우수한 대용량 가성비 — 600정 구성으로 장기간 경제적으로 섭취 가능함.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>상큼한 요거트 맛 — 거부감 없이 매일 맛있게 섭취할 수 있음</t>
+          <t>영국산 원료 신뢰도 — 영국산 원료를 사용한 알려진 브랜드라 믿고 복용함.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>더부룩한 속 케어 — 복용 후 속이 편안해지고 답답함이 감소함</t>
+          <t>위생적인 개별 포장 — 개별 포장 및 정제 형태로 일상 및 여행 시 휴대가 용이함.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -6515,7 +6328,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6523,55 +6336,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>25064</v>
+        <v>466</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>초소형 캡슐 목넘김 — 캡슐 크기가 매우 작아 물과 함께 삼키기 매우 쉬움</t>
+          <t>장 케어 및 체지방 이중 관리 — 체지방 감소와 장 건강을 한 번에 관리할 수 있어 다이어트에 도움 됨.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>질과 장 더블 케어 — 여성 건강에 필요한 유산균 케어를 한 번에 제공함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>귀여운 콜라보 패키지 — 포켓몬 콜라보 및 증정 굿즈의 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>꾸준한 섭취 필요성 — 복용을 중단하면 이너케어 차이가 금방 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>상큼한 요거트 맛 — 상큼한 요거트 맛으로 하루 한 포씩 맛있게 챙겨 먹기 좋음.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -6613,23 +6418,19 @@
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>24219</v>
+        <v>24222</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>아침 공복 장 건강 케어 — 아침 빈속에 섭취 시 장 건강과 면역 유지에 도움 됨</t>
+          <t>장 건강 및 면역 개선 — 아침 공복에 물과 먹으면 장 건강과 면역력 유지에 효과적임.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>하루 1캡슐 간편함 — 매일 한 알로 간편하게 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>실속 있는 기획 구성 — 더블 기획 및 추가 증정 혜택으로 넉넉하게 복용 가능함</t>
-        </is>
-      </c>
+          <t>넉넉한 2개월 복용 용량 — 더블 기획 60캡슐 구성으로 2달 동안 여유 있게 섭취 가능함.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6637,7 +6438,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6645,35 +6446,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,000원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>16677</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6684,7 +6481,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6692,62 +6489,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 Jelly 그린 포켓 젤리 10일 (+2일)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>이너랩</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254481&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025448124ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>41047</v>
+        <v>1209</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>확실한 체력 및 활력 충전 — 피로감이 심할 때 1병으로 활력이 도는 효과가 큼</t>
+          <t>상큼한 키위맛 젤리 — 곤약젤리처럼 탱글하고 상큼하여 간식 대용으로 즐기기 적절함.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>콜라보 굿즈 높은 퀄리티 — 포켓몬 에디션 증정품 디자인과 품질이 훌륭함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>하루 한 병 올인원 — 간편하게 챙겨 먹기 편한 형태임</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>비싼 가격 부담 — 단가가 다소 비싸 지속 구매 시 부담이 될 수 있음</t>
-        </is>
-      </c>
+          <t>소용량 간편 휴대성 — 10포 포장으로 가방이나 파우치에 넣어 다니며 섭취하기 편함.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6755,55 +6544,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>9021</v>
+        <v>8112</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>아침 부종 완화 효과 — 맵단짠 음식 섭취 후나 아침 라인 관리에 유용함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>물 없이 마시는 액상 포 — 작은 용량이라 휴대하고 바로 짜 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>상큼한 포도 맛 — 부담 없는 포도 맛으로 쉽게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>미세한 한약 향 감돌음 — 끝맛에 아주 살짝 한약 느낌이 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>아침 공복 질유산균 루틴 — 기상 후 공복에 챙겨 먹으며 장과 여성 건강 이너뷰티를 케어함.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -6818,54 +6595,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[올영단독] 바이탈뷰티 메타그린 슬림업 120정 (4개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>93,500원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258745&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025874508ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>31250</v>
+        <v>14924</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>식후 체지방 및 혈당 관리 — 고칼로리 식사 후 1알로 혈당과 체지방 감소 보조</t>
+          <t>편리한 젤리 제형 수면케어 — 알약 대신 맛있는 젤리 형태로 자기 전 간편하게 챙김.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고열량 음식 부담 완화 — 배달 음식이나 야식 섭취 시 부담을 줄여줌</t>
+          <t>확실하고 빠른 수면 유도 — 뒤척임 없이 확 푹 잠들게 하여 수면의 질이 향상됨.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>취침 전 양치 재실행 번거로움 — 젤리 형태 특성상 자기 전 섭취 후 다시 양치를 해야 하는 귀찮음이 있음.</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6873,50 +6654,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>18,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>17848</v>
+        <v>16900</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 타사 대비 가격이 저렴하여 장기 복용에 경제적임</t>
+          <t>뱃살 디톡스 및 쾌변 효과 — 화장실을 잘 가도록 도우며 더부룩했던 뱃살을 쏙 들어가게 해 줌.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>하루 한 알 개별 포장 — 개별 포장되어 있어 휴대 및 보관이 용이함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>대기업 브랜드 신뢰도 — 믿을 수 있는 제조사 제품으로 안심하고 먹을 수 있음</t>
-        </is>
-      </c>
+          <t>맛있게 챙기는 체지방 관리 — 굶지 않고 젤리나 음료 형태로 맛있게 체지방을 관리할 수 있음.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -7042,42 +6819,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -7089,52 +6866,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>이너랩</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>대원제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>이너랩</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -7146,52 +6923,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 매드 MAD 10일 (+2일)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[올영단독 증량기획] 셀트리온 홀드잇 매드 MAD 10일 (+2일)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 Jelly 그린 포켓 젤리 10일 (+2일)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 바이탈뷰티 메타그린 슬림업 120정 (4개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -7201,29 +6978,25 @@
           <t>평점</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>4.5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>4.9</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.9</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>5</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
@@ -7238,35 +7011,31 @@
           <t>리뷰수</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>5374</v>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>3088</v>
+        <v>5376</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>467</v>
+        <v>22045</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25064</v>
+        <v>466</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>24219</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>16677</v>
-      </c>
+        <v>24222</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="n">
-        <v>41047</v>
+        <v>1209</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>9021</v>
+        <v>8112</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>31250</v>
+        <v>14924</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>17848</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7275,66 +7044,54 @@
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>수면의 질 개선 보조 — 뒤척임 없이 빠르게 숙면에 들도록 도와줌
-장거리 여행 필수품 — 비행이나 여행 시 수면을 위해 챙기기 좋음
-식물성 안심 원료 — 식약처 인정 식물성 원료로 부담 없이 섭취 가능함</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>하루 1알 간편 관리 — 여러 번 챙길 필요 없이 하루 1알로 관리가 가능함
-우수한 휴대성 — 가방이나 파우치에 넣고 다니기 편함</t>
+          <t>수면 진입 시간 단축 — 한 포 섭취 후 평소보다 훨씬 빠르고 수월하게 잠에 듦.
+장거리 비행 필수템 — 장거리 이동이나 비행 시 편안한 숙면을 취하도록 도움.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>장 케어와 체지방 동시 관리 — 유산균 기능과 다이어트 관리를 동시에 수행함
-상큼한 요거트 맛 — 거부감 없이 매일 맛있게 섭취할 수 있음
-더부룩한 속 케어 — 복용 후 속이 편안해지고 답답함이 감소함</t>
+          <t>우수한 대용량 가성비 — 600정 구성으로 장기간 경제적으로 섭취 가능함.
+영국산 원료 신뢰도 — 영국산 원료를 사용한 알려진 브랜드라 믿고 복용함.
+위생적인 개별 포장 — 개별 포장 및 정제 형태로 일상 및 여행 시 휴대가 용이함.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>초소형 캡슐 목넘김 — 캡슐 크기가 매우 작아 물과 함께 삼키기 매우 쉬움
-질과 장 더블 케어 — 여성 건강에 필요한 유산균 케어를 한 번에 제공함
-귀여운 콜라보 패키지 — 포켓몬 콜라보 및 증정 굿즈의 소장 가치가 높음</t>
+          <t>장 케어 및 체지방 이중 관리 — 체지방 감소와 장 건강을 한 번에 관리할 수 있어 다이어트에 도움 됨.
+상큼한 요거트 맛 — 상큼한 요거트 맛으로 하루 한 포씩 맛있게 챙겨 먹기 좋음.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>아침 공복 장 건강 케어 — 아침 빈속에 섭취 시 장 건강과 면역 유지에 도움 됨
-하루 1캡슐 간편함 — 매일 한 알로 간편하게 챙길 수 있음
-실속 있는 기획 구성 — 더블 기획 및 추가 증정 혜택으로 넉넉하게 복용 가능함</t>
+          <t>장 건강 및 면역 개선 — 아침 공복에 물과 먹으면 장 건강과 면역력 유지에 효과적임.
+넉넉한 2개월 복용 용량 — 더블 기획 60캡슐 구성으로 2달 동안 여유 있게 섭취 가능함.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>확실한 체력 및 활력 충전 — 피로감이 심할 때 1병으로 활력이 도는 효과가 큼
-콜라보 굿즈 높은 퀄리티 — 포켓몬 에디션 증정품 디자인과 품질이 훌륭함
-하루 한 병 올인원 — 간편하게 챙겨 먹기 편한 형태임</t>
+          <t>상큼한 키위맛 젤리 — 곤약젤리처럼 탱글하고 상큼하여 간식 대용으로 즐기기 적절함.
+소용량 간편 휴대성 — 10포 포장으로 가방이나 파우치에 넣어 다니며 섭취하기 편함.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>아침 부종 완화 효과 — 맵단짠 음식 섭취 후나 아침 라인 관리에 유용함
-물 없이 마시는 액상 포 — 작은 용량이라 휴대하고 바로 짜 먹기 편리함
-상큼한 포도 맛 — 부담 없는 포도 맛으로 쉽게 먹을 수 있음</t>
+          <t>아침 공복 질유산균 루틴 — 기상 후 공복에 챙겨 먹으며 장과 여성 건강 이너뷰티를 케어함.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>식후 체지방 및 혈당 관리 — 고칼로리 식사 후 1알로 혈당과 체지방 감소 보조
-고열량 음식 부담 완화 — 배달 음식이나 야식 섭취 시 부담을 줄여줌</t>
+          <t>편리한 젤리 제형 수면케어 — 알약 대신 맛있는 젤리 형태로 자기 전 간편하게 챙김.
+확실하고 빠른 수면 유도 — 뒤척임 없이 확 푹 잠들게 하여 수면의 질이 향상됨.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 타사 대비 가격이 저렴하여 장기 복용에 경제적임
-하루 한 알 개별 포장 — 개별 포장되어 있어 휴대 및 보관이 용이함
-대기업 브랜드 신뢰도 — 믿을 수 있는 제조사 제품으로 안심하고 먹을 수 있음</t>
+          <t>뱃살 디톡스 및 쾌변 효과 — 화장실을 잘 가도록 도우며 더부룩했던 뱃살을 쏙 들어가게 해 줌.
+맛있게 챙기는 체지방 관리 — 굶지 않고 젤리나 음료 형태로 맛있게 체지방을 관리할 수 있음.</t>
         </is>
       </c>
     </row>
@@ -7345,30 +7102,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>섭취 후 복부 온열감 — 원료 특성상 복용 후 속에서 따뜻한 느낌이 들 수 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>꾸준한 섭취 필요성 — 복용을 중단하면 이너케어 차이가 금방 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>비싼 가격 부담 — 단가가 다소 비싸 지속 구매 시 부담이 될 수 있음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>미세한 한약 향 감돌음 — 끝맛에 아주 살짝 한약 느낌이 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 양치 재실행 번거로움 — 젤리 형태 특성상 자기 전 섭취 후 다시 양치를 해야 하는 귀찮음이 있음.</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7379,52 +7124,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>39,800원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>19,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>93,500원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>18,400원</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7554,19 +7299,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -7576,19 +7321,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7604,13 +7349,13 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7620,19 +7365,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -7664,16 +7409,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7698,6 +7443,72 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
